--- a/data/LM6_LMI_Summary.xlsx
+++ b/data/LM6_LMI_Summary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dafha\Work Colleague\OS\Mba rida\Event\MAILER\without raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dafha\Work Colleague\OS\Mba rida\Event\MAILER\new begin_stk\without raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{115ECA13-4CE5-4DB4-9DA0-3D98DF188D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58D5D2A9-F726-4C29-8EF3-1CE687A35430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{F673BAF6-C00D-42EA-9313-7CB2BD08351B}"/>
   </bookViews>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -439,6 +441,9 @@
     <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -513,9 +518,6 @@
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -808,40 +810,40 @@
     <row r="3" spans="1:14">
       <c r="A3" s="39"/>
       <c r="B3" s="39"/>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="I3" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="30" t="s">
+      <c r="K3" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="30" t="s">
+      <c r="L3" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="M3" s="30" t="s">
+      <c r="M3" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="30" t="s">
+      <c r="N3" s="31" t="s">
         <v>73</v>
       </c>
     </row>
@@ -876,16 +878,16 @@
       <c r="J4" s="7">
         <v>197.52498697898361</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="29">
         <v>445</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="29">
         <v>405</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="33">
         <v>91.011235955056179</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="29">
         <v>37</v>
       </c>
     </row>
@@ -920,16 +922,16 @@
       <c r="J5" s="7">
         <v>0</v>
       </c>
-      <c r="K5" s="28">
+      <c r="K5" s="29">
         <v>368</v>
       </c>
-      <c r="L5" s="28">
+      <c r="L5" s="29">
         <v>256</v>
       </c>
-      <c r="M5" s="32">
+      <c r="M5" s="33">
         <v>69.565217391304344</v>
       </c>
-      <c r="N5" s="28">
+      <c r="N5" s="29">
         <v>52</v>
       </c>
     </row>
@@ -964,16 +966,16 @@
       <c r="J6" s="7">
         <v>0</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="29">
         <v>381</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="29">
         <v>284</v>
       </c>
-      <c r="M6" s="32">
+      <c r="M6" s="33">
         <v>74.540682414698168</v>
       </c>
-      <c r="N6" s="28">
+      <c r="N6" s="29">
         <v>17</v>
       </c>
     </row>
@@ -1008,16 +1010,16 @@
       <c r="J7" s="7">
         <v>0</v>
       </c>
-      <c r="K7" s="28">
+      <c r="K7" s="29">
         <v>435</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="29">
         <v>386</v>
       </c>
-      <c r="M7" s="32">
+      <c r="M7" s="33">
         <v>88.735632183908038</v>
       </c>
-      <c r="N7" s="28">
+      <c r="N7" s="29">
         <v>36</v>
       </c>
     </row>
@@ -1052,16 +1054,16 @@
       <c r="J8" s="7">
         <v>0</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="29">
         <v>446</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="29">
         <v>382</v>
       </c>
-      <c r="M8" s="32">
+      <c r="M8" s="33">
         <v>85.650224215246638</v>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="29">
         <v>31</v>
       </c>
     </row>
@@ -1096,16 +1098,16 @@
       <c r="J9" s="7">
         <v>0</v>
       </c>
-      <c r="K9" s="28">
+      <c r="K9" s="29">
         <v>361</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="29">
         <v>282</v>
       </c>
-      <c r="M9" s="32">
+      <c r="M9" s="33">
         <v>78.1163434903047</v>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="29">
         <v>27</v>
       </c>
     </row>
@@ -1140,16 +1142,16 @@
       <c r="J10" s="7">
         <v>0</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="29">
         <v>384</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="29">
         <v>295</v>
       </c>
-      <c r="M10" s="32">
+      <c r="M10" s="33">
         <v>76.822916666666657</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <v>26</v>
       </c>
     </row>
@@ -1184,16 +1186,16 @@
       <c r="J11" s="7">
         <v>0</v>
       </c>
-      <c r="K11" s="28">
+      <c r="K11" s="29">
         <v>374</v>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="29">
         <v>252</v>
       </c>
-      <c r="M11" s="32">
+      <c r="M11" s="33">
         <v>67.379679144385022</v>
       </c>
-      <c r="N11" s="28">
+      <c r="N11" s="29">
         <v>39</v>
       </c>
     </row>
@@ -1228,16 +1230,16 @@
       <c r="J12" s="7">
         <v>0</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="29">
         <v>342</v>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="29">
         <v>258</v>
       </c>
-      <c r="M12" s="32">
+      <c r="M12" s="33">
         <v>75.438596491228068</v>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="29">
         <v>35</v>
       </c>
     </row>
@@ -1272,16 +1274,16 @@
       <c r="J13" s="7">
         <v>0</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="29">
         <v>369</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="29">
         <v>279</v>
       </c>
-      <c r="M13" s="32">
+      <c r="M13" s="33">
         <v>75.609756097560975</v>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="29">
         <v>28</v>
       </c>
     </row>
@@ -1316,16 +1318,16 @@
       <c r="J14" s="7">
         <v>0</v>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="29">
         <v>385</v>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="29">
         <v>295</v>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="33">
         <v>76.623376623376629</v>
       </c>
-      <c r="N14" s="28">
+      <c r="N14" s="29">
         <v>40</v>
       </c>
     </row>
@@ -1360,21 +1362,21 @@
       <c r="J15" s="7">
         <v>0</v>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="29">
         <v>412</v>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="29">
         <v>331</v>
       </c>
-      <c r="M15" s="32">
+      <c r="M15" s="33">
         <v>80.339805825242721</v>
       </c>
-      <c r="N15" s="28">
+      <c r="N15" s="29">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="28" t="s">
         <v>67</v>
       </c>
       <c r="B16" s="1"/>
@@ -1402,21 +1404,21 @@
       <c r="J16" s="7">
         <v>0</v>
       </c>
-      <c r="K16" s="28">
-        <v>0</v>
-      </c>
-      <c r="L16" s="28">
-        <v>0</v>
-      </c>
-      <c r="M16" s="32">
-        <v>0</v>
-      </c>
-      <c r="N16" s="28">
+      <c r="K16" s="29">
+        <v>0</v>
+      </c>
+      <c r="L16" s="29">
+        <v>0</v>
+      </c>
+      <c r="M16" s="33">
+        <v>0</v>
+      </c>
+      <c r="N16" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="28" t="s">
         <v>68</v>
       </c>
       <c r="B17" s="1"/>
@@ -1444,21 +1446,21 @@
       <c r="J17" s="7">
         <v>0</v>
       </c>
-      <c r="K17" s="28">
+      <c r="K17" s="29">
         <v>2</v>
       </c>
-      <c r="L17" s="28">
-        <v>0</v>
-      </c>
-      <c r="M17" s="32">
-        <v>0</v>
-      </c>
-      <c r="N17" s="28">
+      <c r="L17" s="29">
+        <v>0</v>
+      </c>
+      <c r="M17" s="33">
+        <v>0</v>
+      </c>
+      <c r="N17" s="29">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="28" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="1"/>
@@ -1486,60 +1488,60 @@
       <c r="J18" s="7">
         <v>0</v>
       </c>
-      <c r="K18" s="28">
-        <v>0</v>
-      </c>
-      <c r="L18" s="28">
-        <v>0</v>
-      </c>
-      <c r="M18" s="32">
-        <v>0</v>
-      </c>
-      <c r="N18" s="28">
+      <c r="K18" s="29">
+        <v>0</v>
+      </c>
+      <c r="L18" s="29">
+        <v>0</v>
+      </c>
+      <c r="M18" s="33">
+        <v>0</v>
+      </c>
+      <c r="N18" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="14">
         <v>100447.43638700001</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="14">
         <v>93207.286322999993</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="14">
         <v>7240.1500639999995</v>
       </c>
       <c r="F19" s="10">
         <v>9</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="14">
         <v>64519.281584000011</v>
       </c>
       <c r="H19" s="10">
         <v>64.231884759529962</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="14">
         <v>35928.154802999998</v>
       </c>
       <c r="J19" s="10">
         <v>35.768115240470038</v>
       </c>
-      <c r="K19" s="31">
+      <c r="K19" s="32">
         <v>4704</v>
       </c>
-      <c r="L19" s="31">
+      <c r="L19" s="32">
         <v>3705</v>
       </c>
-      <c r="M19" s="33">
+      <c r="M19" s="34">
         <v>78.762755102040813</v>
       </c>
-      <c r="N19" s="31">
+      <c r="N19" s="32">
         <v>420</v>
       </c>
     </row>
@@ -1564,33 +1566,33 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="17.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="15" customWidth="1"/>
-    <col min="3" max="5" width="8.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.7109375" style="15"/>
+    <col min="2" max="2" width="17.140625" style="16" customWidth="1"/>
+    <col min="3" max="5" width="8.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7109375" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="41" t="s">
@@ -1619,40 +1621,40 @@
     <row r="3" spans="1:14">
       <c r="A3" s="41"/>
       <c r="B3" s="41"/>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="29" t="s">
+      <c r="K3" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="29" t="s">
+      <c r="L3" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="M3" s="29" t="s">
+      <c r="M3" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="29" t="s">
+      <c r="N3" s="30" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1660,43 +1662,43 @@
       <c r="A4" s="1">
         <v>31</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="25">
         <v>1284.5642050000001</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="25">
         <v>1170.8403530000001</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="25">
         <v>113.72385199999999</v>
       </c>
       <c r="F4" s="7">
         <v>8.8531076576277474</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="23">
         <v>1284.5642050000001</v>
       </c>
       <c r="H4" s="7">
         <v>100</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="23">
         <v>0</v>
       </c>
       <c r="J4" s="7">
         <v>0</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="35">
         <v>67</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="35">
         <v>58</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="36">
         <v>86.567164179104466</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="37">
         <v>5</v>
       </c>
     </row>
@@ -1704,43 +1706,43 @@
       <c r="A5" s="1">
         <v>32</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>3763.7612260000001</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>3234.6133260000001</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>529.14790000000005</v>
       </c>
       <c r="F5" s="7">
         <v>14.059018843827156</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="23">
         <v>3763.7612260000001</v>
       </c>
       <c r="H5" s="7">
         <v>100</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="23">
         <v>0</v>
       </c>
       <c r="J5" s="7">
         <v>0</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="35">
         <v>107</v>
       </c>
-      <c r="L5" s="34">
+      <c r="L5" s="35">
         <v>86</v>
       </c>
-      <c r="M5" s="35">
+      <c r="M5" s="36">
         <v>80.373831775700936</v>
       </c>
-      <c r="N5" s="36">
+      <c r="N5" s="37">
         <v>13</v>
       </c>
     </row>
@@ -1748,43 +1750,43 @@
       <c r="A6" s="1">
         <v>33</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>3957.095851</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>3291.3131680000001</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>665.78268300000002</v>
       </c>
       <c r="F6" s="7">
         <v>16.825033005752175</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="23">
         <v>3957.095851</v>
       </c>
       <c r="H6" s="7">
         <v>100</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="23">
         <v>0</v>
       </c>
       <c r="J6" s="7">
         <v>0</v>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="35">
         <v>103</v>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="35">
         <v>95</v>
       </c>
-      <c r="M6" s="35">
+      <c r="M6" s="36">
         <v>92.233009708737868</v>
       </c>
-      <c r="N6" s="36">
+      <c r="N6" s="37">
         <v>33</v>
       </c>
     </row>
@@ -1792,43 +1794,43 @@
       <c r="A7" s="1">
         <v>34</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>1913.1155570000001</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>1825.441986</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>87.673570999999995</v>
       </c>
       <c r="F7" s="7">
         <v>4.5827639987143751</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <v>1913.1155570000001</v>
       </c>
       <c r="H7" s="7">
         <v>100</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="23">
         <v>0</v>
       </c>
       <c r="J7" s="7">
         <v>0</v>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="35">
         <v>59</v>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="35">
         <v>59</v>
       </c>
-      <c r="M7" s="35">
+      <c r="M7" s="36">
         <v>100</v>
       </c>
-      <c r="N7" s="36">
+      <c r="N7" s="37">
         <v>8</v>
       </c>
     </row>
@@ -1836,51 +1838,51 @@
       <c r="A8" s="1">
         <v>35</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>4827.3093840000001</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>4164.287335</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>663.02204900000004</v>
       </c>
       <c r="F8" s="7">
         <v>13.734815738091505</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="23">
         <v>4827.3039779999999</v>
       </c>
       <c r="H8" s="7">
         <v>99.999888012149825</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="23">
         <v>5.4060000000000002E-3</v>
       </c>
       <c r="J8" s="7">
         <v>1.1198797557886048E-4</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="35">
         <v>469</v>
       </c>
-      <c r="L8" s="34">
+      <c r="L8" s="35">
         <v>423</v>
       </c>
-      <c r="M8" s="35">
+      <c r="M8" s="36">
         <v>90.191897654584224</v>
       </c>
-      <c r="N8" s="36">
+      <c r="N8" s="37">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="21" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="2">
@@ -1913,7 +1915,7 @@
       <c r="L9" s="2">
         <v>721</v>
       </c>
-      <c r="M9" s="37">
+      <c r="M9" s="38">
         <v>89.565217391304358</v>
       </c>
       <c r="N9" s="2">
@@ -1924,43 +1926,43 @@
       <c r="A10" s="1">
         <v>80</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>2007.7145949999999</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>1955.274766</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>52.439829000000003</v>
       </c>
       <c r="F10" s="7">
         <v>2.6119165109720193</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="23">
         <v>2007.7145949999999</v>
       </c>
       <c r="H10" s="7">
         <v>100</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="23">
         <v>0</v>
       </c>
       <c r="J10" s="7">
         <v>0</v>
       </c>
-      <c r="K10" s="34">
+      <c r="K10" s="35">
         <v>92</v>
       </c>
-      <c r="L10" s="34">
+      <c r="L10" s="35">
         <v>82</v>
       </c>
-      <c r="M10" s="35">
+      <c r="M10" s="36">
         <v>89.130434782608688</v>
       </c>
-      <c r="N10" s="36">
+      <c r="N10" s="37">
         <v>85</v>
       </c>
     </row>
@@ -1968,51 +1970,51 @@
       <c r="A11" s="1">
         <v>82</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <v>3164.090346</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <v>3089.217365</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <v>74.872980999999996</v>
       </c>
       <c r="F11" s="7">
         <v>2.3663351172842897</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="23">
         <v>3164.083138</v>
       </c>
       <c r="H11" s="7">
         <v>99.999772193609786</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="23">
         <v>7.208E-3</v>
       </c>
       <c r="J11" s="7">
         <v>2.2780690916219534E-4</v>
       </c>
-      <c r="K11" s="34">
+      <c r="K11" s="35">
         <v>23</v>
       </c>
-      <c r="L11" s="34">
+      <c r="L11" s="35">
         <v>19</v>
       </c>
-      <c r="M11" s="35">
+      <c r="M11" s="36">
         <v>82.608695652173907</v>
       </c>
-      <c r="N11" s="36">
+      <c r="N11" s="37">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="21" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="2">
@@ -2045,7 +2047,7 @@
       <c r="L12" s="2">
         <v>101</v>
       </c>
-      <c r="M12" s="37">
+      <c r="M12" s="38">
         <v>87.826086956521749</v>
       </c>
       <c r="N12" s="2">
@@ -2056,43 +2058,43 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>4170.0383039999997</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>3788.7711549999999</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>381.26714900000002</v>
       </c>
       <c r="F13" s="7">
         <v>9.1430131141548401</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="23">
         <v>3295.8251939999996</v>
       </c>
       <c r="H13" s="7">
         <v>79.035849403075403</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="23">
         <v>874.21311000000003</v>
       </c>
       <c r="J13" s="7">
         <v>26.524862774624452</v>
       </c>
-      <c r="K13" s="34">
+      <c r="K13" s="35">
         <v>269</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="35">
         <v>215</v>
       </c>
-      <c r="M13" s="35">
+      <c r="M13" s="36">
         <v>79.925650557620827</v>
       </c>
-      <c r="N13" s="36">
+      <c r="N13" s="37">
         <v>29</v>
       </c>
     </row>
@@ -2100,43 +2102,43 @@
       <c r="A14" s="1">
         <v>17</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <v>16957.165378999998</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>16075.582547</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>881.58283200000005</v>
       </c>
       <c r="F14" s="7">
         <v>5.1988808995857596</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="23">
         <v>10229.346570999998</v>
       </c>
       <c r="H14" s="7">
         <v>60.324625857976066</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="23">
         <v>6727.818808</v>
       </c>
       <c r="J14" s="7">
         <v>65.769780711831942</v>
       </c>
-      <c r="K14" s="34">
+      <c r="K14" s="35">
         <v>289</v>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="35">
         <v>254</v>
       </c>
-      <c r="M14" s="35">
+      <c r="M14" s="36">
         <v>87.889273356401389</v>
       </c>
-      <c r="N14" s="36">
+      <c r="N14" s="37">
         <v>17</v>
       </c>
     </row>
@@ -2144,43 +2146,43 @@
       <c r="A15" s="1">
         <v>21</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="24">
+      <c r="B15" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="25">
         <v>11208.278643</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <v>11058.407134999999</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>149.87150800000001</v>
       </c>
       <c r="F15" s="7">
         <v>1.3371500903361331</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="23">
         <v>3853.6376700000001</v>
       </c>
       <c r="H15" s="7">
         <v>34.382065192559651</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="23">
         <v>7354.6409729999996</v>
       </c>
       <c r="J15" s="7">
         <v>190.84931181399833</v>
       </c>
-      <c r="K15" s="34">
+      <c r="K15" s="35">
         <v>347</v>
       </c>
-      <c r="L15" s="34">
+      <c r="L15" s="35">
         <v>309</v>
       </c>
-      <c r="M15" s="35">
+      <c r="M15" s="36">
         <v>89.04899135446685</v>
       </c>
-      <c r="N15" s="36">
+      <c r="N15" s="37">
         <v>14</v>
       </c>
     </row>
@@ -2188,43 +2190,43 @@
       <c r="A16" s="1">
         <v>23</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>21010.670886</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>19445.830981999999</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>1564.8399039999999</v>
       </c>
       <c r="F16" s="7">
         <v>7.4478340672248438</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <v>7852.2970129999994</v>
       </c>
       <c r="H16" s="7">
         <v>37.372899968806827</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="23">
         <v>13158.373873</v>
       </c>
       <c r="J16" s="7">
         <v>167.5735628850442</v>
       </c>
-      <c r="K16" s="34">
+      <c r="K16" s="35">
         <v>963</v>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="35">
         <v>703</v>
       </c>
-      <c r="M16" s="35">
+      <c r="M16" s="36">
         <v>73.001038421599176</v>
       </c>
-      <c r="N16" s="36">
+      <c r="N16" s="37">
         <v>80</v>
       </c>
     </row>
@@ -2232,51 +2234,51 @@
       <c r="A17" s="1">
         <v>24</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="25">
         <v>3373.6741240000001</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <v>3041.1996250000002</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <v>332.47449899999998</v>
       </c>
       <c r="F17" s="7">
         <v>9.8549678119415169</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="23">
         <v>2519.7065470000002</v>
       </c>
       <c r="H17" s="7">
         <v>74.687312834249326</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="23">
         <v>853.96757700000001</v>
       </c>
       <c r="J17" s="7">
         <v>33.891548919327384</v>
       </c>
-      <c r="K17" s="34">
+      <c r="K17" s="35">
         <v>530</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="35">
         <v>321</v>
       </c>
-      <c r="M17" s="35">
+      <c r="M17" s="36">
         <v>60.566037735849051</v>
       </c>
-      <c r="N17" s="36">
+      <c r="N17" s="37">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3">
@@ -2309,7 +2311,7 @@
       <c r="L18" s="3">
         <v>1802</v>
       </c>
-      <c r="M18" s="37">
+      <c r="M18" s="38">
         <v>75.145954962468721</v>
       </c>
       <c r="N18" s="3">
@@ -2320,43 +2322,43 @@
       <c r="A19" s="1">
         <v>14</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <v>9281.448468999999</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="25">
         <v>8344.2955469999997</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <v>937.15292199999999</v>
       </c>
       <c r="F19" s="7">
         <v>10.097054626011092</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="23">
         <v>6410.300103999999</v>
       </c>
       <c r="H19" s="7">
         <v>69.065729615483789</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="23">
         <v>2871.148365</v>
       </c>
       <c r="J19" s="7">
         <v>44.789609197990842</v>
       </c>
-      <c r="K19" s="34">
+      <c r="K19" s="35">
         <v>555</v>
       </c>
-      <c r="L19" s="34">
+      <c r="L19" s="35">
         <v>485</v>
       </c>
-      <c r="M19" s="35">
+      <c r="M19" s="36">
         <v>87.387387387387378</v>
       </c>
-      <c r="N19" s="36">
+      <c r="N19" s="37">
         <v>16</v>
       </c>
     </row>
@@ -2364,51 +2366,51 @@
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="25">
         <v>7862.3551120000002</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="25">
         <v>7122.9128479999999</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <v>739.44226400000002</v>
       </c>
       <c r="F20" s="7">
         <v>9.4048443941614721</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="23">
         <v>3900.509869</v>
       </c>
       <c r="H20" s="7">
         <v>49.609942738999493</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="23">
         <v>3961.8452430000002</v>
       </c>
       <c r="J20" s="7">
         <v>101.572496316122</v>
       </c>
-      <c r="K20" s="34">
+      <c r="K20" s="35">
         <v>682</v>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="35">
         <v>483</v>
       </c>
-      <c r="M20" s="35">
+      <c r="M20" s="36">
         <v>70.821114369501473</v>
       </c>
-      <c r="N20" s="36">
+      <c r="N20" s="37">
         <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="21" t="s">
         <v>63</v>
       </c>
       <c r="C21" s="3">
@@ -2441,7 +2443,7 @@
       <c r="L21" s="3">
         <v>968</v>
       </c>
-      <c r="M21" s="37">
+      <c r="M21" s="38">
         <v>78.253839935327406</v>
       </c>
       <c r="N21" s="3">
@@ -2452,43 +2454,43 @@
       <c r="A22" s="1">
         <v>86</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="25">
         <v>1457.48215</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="25">
         <v>1457.48215</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="25">
         <v>0</v>
       </c>
       <c r="F22" s="7">
         <v>0</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="23">
         <v>1457.48215</v>
       </c>
       <c r="H22" s="7">
         <v>100</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="23">
         <v>0</v>
       </c>
       <c r="J22" s="7">
         <v>0</v>
       </c>
-      <c r="K22" s="34">
-        <v>0</v>
-      </c>
-      <c r="L22" s="34">
-        <v>0</v>
-      </c>
-      <c r="M22" s="35">
-        <v>0</v>
-      </c>
-      <c r="N22" s="36">
+      <c r="K22" s="35">
+        <v>0</v>
+      </c>
+      <c r="L22" s="35">
+        <v>0</v>
+      </c>
+      <c r="M22" s="36">
+        <v>0</v>
+      </c>
+      <c r="N22" s="37">
         <v>0</v>
       </c>
     </row>
@@ -2496,43 +2498,43 @@
       <c r="A23" s="1">
         <v>87</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="25">
         <v>167.988981</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="25">
         <v>162.99618799999999</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="25">
         <v>4.9927929999999998</v>
       </c>
       <c r="F23" s="7">
         <v>2.9720955328611702</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="23">
         <v>167.988981</v>
       </c>
       <c r="H23" s="7">
         <v>100</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="23">
         <v>0</v>
       </c>
       <c r="J23" s="7">
         <v>0</v>
       </c>
-      <c r="K23" s="34">
+      <c r="K23" s="35">
         <v>12</v>
       </c>
-      <c r="L23" s="34">
+      <c r="L23" s="35">
         <v>7</v>
       </c>
-      <c r="M23" s="35">
+      <c r="M23" s="36">
         <v>58.333333333333336</v>
       </c>
-      <c r="N23" s="36">
+      <c r="N23" s="37">
         <v>0</v>
       </c>
     </row>
@@ -2540,51 +2542,51 @@
       <c r="A24" s="1">
         <v>88</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="25">
         <v>609.83027100000004</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="25">
         <v>609.83027100000004</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="25">
         <v>0</v>
       </c>
       <c r="F24" s="7">
         <v>0</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="23">
         <v>483.70414400000004</v>
       </c>
       <c r="H24" s="7">
         <v>79.317831042860774</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="23">
         <v>126.126127</v>
       </c>
       <c r="J24" s="7">
         <v>26.07505611942824</v>
       </c>
-      <c r="K24" s="34">
-        <v>0</v>
-      </c>
-      <c r="L24" s="34">
-        <v>0</v>
-      </c>
-      <c r="M24" s="35">
-        <v>0</v>
-      </c>
-      <c r="N24" s="36">
+      <c r="K24" s="35">
+        <v>0</v>
+      </c>
+      <c r="L24" s="35">
+        <v>0</v>
+      </c>
+      <c r="M24" s="36">
+        <v>0</v>
+      </c>
+      <c r="N24" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="21" t="s">
         <v>64</v>
       </c>
       <c r="C25" s="3">
@@ -2617,7 +2619,7 @@
       <c r="L25" s="3">
         <v>7</v>
       </c>
-      <c r="M25" s="37">
+      <c r="M25" s="38">
         <v>58.333333333333336</v>
       </c>
       <c r="N25" s="3">
@@ -2628,43 +2630,43 @@
       <c r="A26" s="1">
         <v>51</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="25">
         <v>738.86272499999995</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="25">
         <v>716.61083399999995</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="25">
         <v>22.251891000000001</v>
       </c>
       <c r="F26" s="7">
         <v>3.0116407618208108</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="23">
         <v>738.86272499999995</v>
       </c>
       <c r="H26" s="7">
         <v>100</v>
       </c>
-      <c r="I26" s="22">
+      <c r="I26" s="23">
         <v>0</v>
       </c>
       <c r="J26" s="7">
         <v>0</v>
       </c>
-      <c r="K26" s="34">
+      <c r="K26" s="35">
         <v>45</v>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="35">
         <v>35</v>
       </c>
-      <c r="M26" s="35">
+      <c r="M26" s="36">
         <v>77.777777777777786</v>
       </c>
-      <c r="N26" s="36">
+      <c r="N26" s="37">
         <v>1</v>
       </c>
     </row>
@@ -2672,43 +2674,43 @@
       <c r="A27" s="1">
         <v>57</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="25">
         <v>606.943939</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="25">
         <v>601.41421000000003</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="25">
         <v>5.5297289999999997</v>
       </c>
       <c r="F27" s="7">
         <v>0.911077390295844</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="23">
         <v>606.943939</v>
       </c>
       <c r="H27" s="7">
         <v>100</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="23">
         <v>0</v>
       </c>
       <c r="J27" s="7">
         <v>0</v>
       </c>
-      <c r="K27" s="34">
+      <c r="K27" s="35">
         <v>11</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="35">
         <v>10</v>
       </c>
-      <c r="M27" s="35">
+      <c r="M27" s="36">
         <v>90.909090909090907</v>
       </c>
-      <c r="N27" s="36">
+      <c r="N27" s="37">
         <v>0</v>
       </c>
     </row>
@@ -2716,43 +2718,43 @@
       <c r="A28" s="1">
         <v>85</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="25">
         <v>336.677415</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="25">
         <v>323.65426200000002</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="25">
         <v>13.023153000000001</v>
       </c>
       <c r="F28" s="7">
         <v>3.8681397740920636</v>
       </c>
-      <c r="G28" s="22">
+      <c r="G28" s="23">
         <v>336.677415</v>
       </c>
       <c r="H28" s="7">
         <v>100</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28" s="23">
         <v>0</v>
       </c>
       <c r="J28" s="7">
         <v>0</v>
       </c>
-      <c r="K28" s="34">
+      <c r="K28" s="35">
         <v>37</v>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="35">
         <v>36</v>
       </c>
-      <c r="M28" s="35">
+      <c r="M28" s="36">
         <v>97.297297297297305</v>
       </c>
-      <c r="N28" s="36">
+      <c r="N28" s="37">
         <v>1</v>
       </c>
     </row>
@@ -2760,43 +2762,43 @@
       <c r="A29" s="1">
         <v>13</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="25">
         <v>197.30259699999999</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="25">
         <v>176.24404200000001</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="25">
         <v>21.058554999999998</v>
       </c>
       <c r="F29" s="7">
         <v>10.673227479109157</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="23">
         <v>197.30259699999999</v>
       </c>
       <c r="H29" s="7">
         <v>100</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29" s="23">
         <v>0</v>
       </c>
       <c r="J29" s="7">
         <v>0</v>
       </c>
-      <c r="K29" s="34">
+      <c r="K29" s="35">
         <v>44</v>
       </c>
-      <c r="L29" s="34">
+      <c r="L29" s="35">
         <v>26</v>
       </c>
-      <c r="M29" s="35">
+      <c r="M29" s="36">
         <v>59.090909090909093</v>
       </c>
-      <c r="N29" s="36">
+      <c r="N29" s="37">
         <v>1</v>
       </c>
     </row>
@@ -2804,43 +2806,43 @@
       <c r="A30" s="1">
         <v>62</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="25">
         <v>643.52623500000004</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="25">
         <v>643.52623500000004</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="25">
         <v>0</v>
       </c>
       <c r="F30" s="7">
         <v>0</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="23">
         <v>643.52623500000004</v>
       </c>
       <c r="H30" s="7">
         <v>100</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30" s="23">
         <v>0</v>
       </c>
       <c r="J30" s="7">
         <v>0</v>
       </c>
-      <c r="K30" s="34">
-        <v>0</v>
-      </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="35">
-        <v>0</v>
-      </c>
-      <c r="N30" s="36">
+      <c r="K30" s="35">
+        <v>0</v>
+      </c>
+      <c r="L30" s="35">
+        <v>0</v>
+      </c>
+      <c r="M30" s="36">
+        <v>0</v>
+      </c>
+      <c r="N30" s="37">
         <v>0</v>
       </c>
     </row>
@@ -2848,51 +2850,51 @@
       <c r="A31" s="1">
         <v>71</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="25">
         <v>902.02473199999997</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="25">
         <v>902.02473199999997</v>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="25">
         <v>0</v>
       </c>
       <c r="F31" s="7">
         <v>0</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="23">
         <v>902.01661899999999</v>
       </c>
       <c r="H31" s="7">
         <v>99.999100578985008</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="23">
         <v>8.1130000000000004E-3</v>
       </c>
       <c r="J31" s="7">
         <v>8.9942910464269402E-4</v>
       </c>
-      <c r="K31" s="34">
-        <v>0</v>
-      </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35">
-        <v>0</v>
-      </c>
-      <c r="N31" s="36">
+      <c r="K31" s="35">
+        <v>0</v>
+      </c>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="36">
+        <v>0</v>
+      </c>
+      <c r="N31" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="21" t="s">
         <v>21</v>
       </c>
       <c r="C32" s="3">
@@ -2925,7 +2927,7 @@
       <c r="L32" s="3">
         <v>107</v>
       </c>
-      <c r="M32" s="37">
+      <c r="M32" s="38">
         <v>78.102189781021906</v>
       </c>
       <c r="N32" s="3">
@@ -2936,43 +2938,43 @@
       <c r="A33" s="1">
         <v>97</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="25">
         <v>5.5152549999999998</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="25">
         <v>5.5152549999999998</v>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="25">
         <v>0</v>
       </c>
       <c r="F33" s="7">
         <v>0</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="23">
         <v>5.5152549999999998</v>
       </c>
       <c r="H33" s="7">
         <v>100</v>
       </c>
-      <c r="I33" s="22">
+      <c r="I33" s="23">
         <v>0</v>
       </c>
       <c r="J33" s="7">
         <v>0</v>
       </c>
-      <c r="K33" s="34">
-        <v>0</v>
-      </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35">
-        <v>0</v>
-      </c>
-      <c r="N33" s="36">
+      <c r="K33" s="35">
+        <v>0</v>
+      </c>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="36">
+        <v>0</v>
+      </c>
+      <c r="N33" s="37">
         <v>0</v>
       </c>
     </row>
@@ -2980,43 +2982,43 @@
       <c r="A34" s="1">
         <v>98</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="24">
-        <v>0</v>
-      </c>
-      <c r="D34" s="24">
-        <v>0</v>
-      </c>
-      <c r="E34" s="24">
+      <c r="C34" s="25">
+        <v>0</v>
+      </c>
+      <c r="D34" s="25">
+        <v>0</v>
+      </c>
+      <c r="E34" s="25">
         <v>0</v>
       </c>
       <c r="F34" s="7">
         <v>0</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="23">
         <v>0</v>
       </c>
       <c r="H34" s="7">
         <v>0</v>
       </c>
-      <c r="I34" s="22">
+      <c r="I34" s="23">
         <v>0</v>
       </c>
       <c r="J34" s="7">
         <v>0</v>
       </c>
-      <c r="K34" s="34">
-        <v>0</v>
-      </c>
-      <c r="L34" s="34">
-        <v>0</v>
-      </c>
-      <c r="M34" s="35">
-        <v>0</v>
-      </c>
-      <c r="N34" s="36">
+      <c r="K34" s="35">
+        <v>0</v>
+      </c>
+      <c r="L34" s="35">
+        <v>0</v>
+      </c>
+      <c r="M34" s="36">
+        <v>0</v>
+      </c>
+      <c r="N34" s="37">
         <v>0</v>
       </c>
     </row>
@@ -3024,51 +3026,51 @@
       <c r="A35" s="1">
         <v>99</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="25">
         <v>6.0000000000000002E-6</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="25">
         <v>6.0000000000000002E-6</v>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="25">
         <v>0</v>
       </c>
       <c r="F35" s="7">
         <v>0</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="23">
         <v>6.0000000000000002E-6</v>
       </c>
       <c r="H35" s="7">
         <v>100</v>
       </c>
-      <c r="I35" s="22">
+      <c r="I35" s="23">
         <v>0</v>
       </c>
       <c r="J35" s="7">
         <v>0</v>
       </c>
-      <c r="K35" s="34">
-        <v>0</v>
-      </c>
-      <c r="L35" s="34">
-        <v>0</v>
-      </c>
-      <c r="M35" s="35">
-        <v>0</v>
-      </c>
-      <c r="N35" s="36">
+      <c r="K35" s="35">
+        <v>0</v>
+      </c>
+      <c r="L35" s="35">
+        <v>0</v>
+      </c>
+      <c r="M35" s="36">
+        <v>0</v>
+      </c>
+      <c r="N35" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="22" t="s">
         <v>51</v>
       </c>
       <c r="C36" s="3">
@@ -3101,7 +3103,7 @@
       <c r="L36" s="3">
         <v>3706</v>
       </c>
-      <c r="M36" s="37">
+      <c r="M36" s="38">
         <v>78.784013605442169</v>
       </c>
       <c r="N36" s="3">
